--- a/data/sars/pacific/tables/Pacific_2008_Appendix3.xlsx
+++ b/data/sars/pacific/tables/Pacific_2008_Appendix3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/pacific/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87845973-9729-9B4B-9726-5CF7F32DD23E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD84DEE-336F-8342-9905-0492AF8F46CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="500" windowWidth="32040" windowHeight="20180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="103">
   <si>
     <t>California sea lion</t>
   </si>
@@ -404,9 +404,6 @@
     <t>survey3</t>
   </si>
   <si>
-    <t>revised</t>
-  </si>
-  <si>
     <t>PIC</t>
   </si>
   <si>
@@ -414,6 +411,15 @@
   </si>
   <si>
     <t>rf</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>revision_yr</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -865,12 +871,12 @@
     <col min="11" max="11" width="13.3984375" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.59765625" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="15" width="8.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.19921875" style="2" customWidth="1"/>
     <col min="17" max="21" width="24.19921875" style="2" customWidth="1"/>
     <col min="22" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="20" customFormat="1" ht="16" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" s="20" customFormat="1" ht="32" x14ac:dyDescent="0.15">
       <c r="A1" s="19" t="s">
         <v>83</v>
       </c>
@@ -893,7 +899,7 @@
         <v>89</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I1" s="19" t="s">
         <v>90</v>
@@ -917,9 +923,11 @@
         <v>96</v>
       </c>
       <c r="P1" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q1" s="19"/>
+        <v>101</v>
+      </c>
+      <c r="Q1" s="19" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="2" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
@@ -1261,13 +1269,13 @@
     </row>
     <row r="9" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A9" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>55</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D9" s="12">
         <v>1208</v>
@@ -1307,6 +1315,9 @@
       </c>
       <c r="P9" s="11">
         <v>2008</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="16" x14ac:dyDescent="0.15">
@@ -1658,8 +1669,11 @@
       <c r="P16" s="16">
         <v>2008</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" ht="16" x14ac:dyDescent="0.15">
+      <c r="Q16" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A17" s="11" t="s">
         <v>24</v>
       </c>
@@ -1708,8 +1722,11 @@
       <c r="P17" s="16">
         <v>2008</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="16" x14ac:dyDescent="0.15">
+      <c r="Q17" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -1758,8 +1775,11 @@
       <c r="P18" s="16">
         <v>2008</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" ht="16" x14ac:dyDescent="0.15">
+      <c r="Q18" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A19" s="11" t="s">
         <v>26</v>
       </c>
@@ -1808,8 +1828,11 @@
       <c r="P19" s="16">
         <v>2008</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" ht="16" x14ac:dyDescent="0.15">
+      <c r="Q19" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A20" s="11" t="s">
         <v>26</v>
       </c>
@@ -1858,8 +1881,11 @@
       <c r="P20" s="16">
         <v>2008</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" ht="16" x14ac:dyDescent="0.15">
+      <c r="Q20" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -1908,8 +1934,11 @@
       <c r="P21" s="16">
         <v>2008</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" ht="16" x14ac:dyDescent="0.15">
+      <c r="Q21" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A22" s="11" t="s">
         <v>30</v>
       </c>
@@ -1958,8 +1987,11 @@
       <c r="P22" s="16">
         <v>2008</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" ht="16" x14ac:dyDescent="0.15">
+      <c r="Q22" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A23" s="11" t="s">
         <v>31</v>
       </c>
@@ -2008,8 +2040,11 @@
       <c r="P23" s="16">
         <v>2008</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" ht="16" x14ac:dyDescent="0.15">
+      <c r="Q23" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A24" s="11" t="s">
         <v>32</v>
       </c>
@@ -2058,8 +2093,11 @@
       <c r="P24" s="16">
         <v>2008</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" ht="16" x14ac:dyDescent="0.15">
+      <c r="Q24" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A25" s="11" t="s">
         <v>33</v>
       </c>
@@ -2108,8 +2146,11 @@
       <c r="P25" s="16">
         <v>2008</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" ht="16" x14ac:dyDescent="0.15">
+      <c r="Q25" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A26" s="11" t="s">
         <v>33</v>
       </c>
@@ -2158,8 +2199,11 @@
       <c r="P26" s="16">
         <v>2008</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" ht="16" x14ac:dyDescent="0.15">
+      <c r="Q26" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A27" s="11" t="s">
         <v>37</v>
       </c>
@@ -2208,8 +2252,11 @@
       <c r="P27" s="16">
         <v>2008</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" ht="16" x14ac:dyDescent="0.15">
+      <c r="Q27" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A28" s="11" t="s">
         <v>38</v>
       </c>
@@ -2258,8 +2305,11 @@
       <c r="P28" s="16">
         <v>2008</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" ht="16" x14ac:dyDescent="0.15">
+      <c r="Q28" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A29" s="11" t="s">
         <v>39</v>
       </c>
@@ -2308,8 +2358,11 @@
       <c r="P29" s="16">
         <v>2008</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" ht="16" x14ac:dyDescent="0.15">
+      <c r="Q29" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A30" s="11" t="s">
         <v>40</v>
       </c>
@@ -2358,8 +2411,11 @@
       <c r="P30" s="16">
         <v>2008</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" ht="16" x14ac:dyDescent="0.15">
+      <c r="Q30" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A31" s="11" t="s">
         <v>41</v>
       </c>
@@ -2408,8 +2464,11 @@
       <c r="P31" s="16">
         <v>2008</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" ht="16" x14ac:dyDescent="0.15">
+      <c r="Q31" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A32" s="11" t="s">
         <v>45</v>
       </c>
@@ -2457,6 +2516,9 @@
       </c>
       <c r="P32" s="16">
         <v>2008</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="16" x14ac:dyDescent="0.15">
@@ -2508,6 +2570,9 @@
       <c r="P33" s="16">
         <v>2008</v>
       </c>
+      <c r="Q33" s="2" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="34" spans="1:18" ht="16" x14ac:dyDescent="0.15">
       <c r="A34" s="11" t="s">
@@ -2558,6 +2623,9 @@
       <c r="P34" s="16">
         <v>2008</v>
       </c>
+      <c r="Q34" s="2" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="35" spans="1:18" ht="16" x14ac:dyDescent="0.15">
       <c r="A35" s="11" t="s">
@@ -2608,6 +2676,9 @@
       <c r="P35" s="16">
         <v>2008</v>
       </c>
+      <c r="Q35" s="2" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="36" spans="1:18" ht="16" x14ac:dyDescent="0.15">
       <c r="A36" s="11" t="s">
@@ -2658,6 +2729,9 @@
       <c r="P36" s="16">
         <v>2008</v>
       </c>
+      <c r="Q36" s="2" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="37" spans="1:18" ht="16" x14ac:dyDescent="0.15">
       <c r="A37" s="11" t="s">
@@ -2708,6 +2782,9 @@
       <c r="P37" s="16">
         <v>2008</v>
       </c>
+      <c r="Q37" s="2" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="38" spans="1:18" ht="16" x14ac:dyDescent="0.15">
       <c r="A38" s="11" t="s">
@@ -2758,6 +2835,9 @@
       <c r="P38" s="16">
         <v>2008</v>
       </c>
+      <c r="Q38" s="2" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="39" spans="1:18" ht="16" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
@@ -3256,7 +3336,9 @@
       <c r="P48" s="16">
         <v>2008</v>
       </c>
-      <c r="Q48" s="17"/>
+      <c r="Q48" s="2" t="s">
+        <v>102</v>
+      </c>
       <c r="R48" s="17"/>
     </row>
     <row r="49" spans="1:18" ht="16" x14ac:dyDescent="0.15">
@@ -3304,7 +3386,9 @@
       <c r="P49" s="16">
         <v>2008</v>
       </c>
-      <c r="Q49" s="7"/>
+      <c r="Q49" s="2" t="s">
+        <v>102</v>
+      </c>
       <c r="R49" s="7"/>
     </row>
     <row r="50" spans="1:18" ht="16" x14ac:dyDescent="0.15">
@@ -3356,7 +3440,9 @@
       <c r="P50" s="16">
         <v>2008</v>
       </c>
-      <c r="Q50" s="7"/>
+      <c r="Q50" s="2" t="s">
+        <v>102</v>
+      </c>
       <c r="R50" s="7"/>
     </row>
     <row r="51" spans="1:18" ht="16" x14ac:dyDescent="0.2">
